--- a/Noir Wingman/Assets/Sheets/Demo Dialogue/Eoin Richardson/Rookie_Intro_1.xlsx
+++ b/Noir Wingman/Assets/Sheets/Demo Dialogue/Eoin Richardson/Rookie_Intro_1.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b685ca5cabcdd482/Desktop/NoirWingman/Noir Wingman/Assets/Sheets/Demo Dialogue/Eoin Richardson/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FD02AAB5-D4B2-4B67-A133-2A3674DA34EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0CECD4E8-31A9-4995-8D99-03DDB6BEEFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{A85544C4-B6D9-419A-8FBF-C64C862E95D0}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Rookie_Intro_1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -92,9 +92,6 @@
     <t>Null</t>
   </si>
   <si>
-    <t>*A fresh-faced young man with a crisply pressed GPD uniform underneath a ratty coat clearly handed down from a much larger owner. He shifts uncomfortably in his seat as he glances around at both colleagues and criminals.|Howdy ma’am. You're Julia, right? |*The expression on his face toes the thin line between judgement and genuine curiosity.|Call me Jules, if you don’t mind. Who’re you?|Eoin Richardson. I’m-uh- Diggums’ new partner.|*Huh. Interesting. Let's see how this goes.|Nice to meet you, Eoin. I was wondering if I could ask you a couple questions? You’re not in any kind of trouble- I just make sure the guy my partner’s working with is trustworthy.|Hm? I’d promise you that I am, but from what Diggums’s told me, that wouldn’t be enough for you. That is to say, ask away.</t>
-  </si>
-  <si>
     <t>Neutral|Neutral|Neutral|Neutral|Sad|Sad|Happy|Angry</t>
   </si>
   <si>
@@ -102,6 +99,9 @@
   </si>
   <si>
     <t>Eoin Richardson|Eoin Richardson|Eoin Richardson|Detective Juels|Eoin Richardson|Detective Juels|Detective Juels|Eoin Richardson</t>
+  </si>
+  <si>
+    <t>*A fresh-faced young man with a crisply pressed GPD uniform underneath a ratty coat clearly handed down from a much larger owner. He shifts uncomfortably in his seat as he glances around at both colleagues and criminals.|Howdy ma'am. You're Julia, right? |*The expression on his face toes the thin line between judgement and genuine curiosity.|Call me Jules, if you don't mind. Who're you?|Eoin Richardson. I'm-uh- Diggums' new partner.|*Huh. Interesting. Let's see how this goes.|Nice to meet you, Eoin. I was wondering if I could ask you a couple questions? You're not in any kind of trouble- I just make sure the guy my partner's working with is trustworthy.|Hm? I'd promise you that I am, but from what Diggums's told me, that wouldn't be enough for you. That is to say, ask away.</t>
   </si>
 </sst>
 </file>
@@ -545,10 +545,10 @@
         <v>15</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>17</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>18</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>16</v>
@@ -569,10 +569,10 @@
         <v>0</v>
       </c>
       <c r="K2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="M2" s="1">
         <v>0</v>
